--- a/25-06-26/Umair.xlsx
+++ b/25-06-26/Umair.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AA74972-8E92-4173-B343-1540C790DEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F06CF7-5A42-4476-B461-9F02B1CA37EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="123">
   <si>
     <t>Gm</t>
   </si>
@@ -410,6 +410,9 @@
   </si>
   <si>
     <t>34193677367-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promis Monday </t>
   </si>
 </sst>
 </file>
@@ -3384,7 +3387,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -3412,7 +3415,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -4617,7 +4620,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -4645,7 +4648,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -5838,7 +5841,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -5866,7 +5869,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -7059,7 +7062,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -7087,7 +7090,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -8280,7 +8283,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -8308,7 +8311,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -9501,7 +9504,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -9529,7 +9532,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -10719,7 +10722,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -10747,7 +10750,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -11936,7 +11939,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -11964,7 +11967,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -13153,7 +13156,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -13181,7 +13184,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -14370,7 +14373,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -14398,7 +14401,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -18337,7 +18340,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -18365,7 +18368,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -19554,7 +19557,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -19582,7 +19585,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -20771,7 +20774,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -20799,7 +20802,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -21988,7 +21991,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -22016,7 +22019,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -23210,7 +23213,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -23238,7 +23241,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -23535,15 +23538,15 @@
       <c r="G16" s="114"/>
       <c r="H16" s="172">
         <f>+'1'!H16+'2'!H16+'4'!H16+'3'!H16+'5'!H16+'6'!H16+'7'!H16+'8'!H16+'9'!H16+'10'!H16+'11'!H16+'12'!H16+'13'!H16+'14'!H16+'15'!H16+'16'!H16</f>
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="I16" s="1">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>3147.75</v>
+        <v>1049.25</v>
       </c>
       <c r="J16" s="172">
         <f>+'1'!J16+'2'!J16+'4'!J16+'3'!J16+'5'!J16+'6'!J16+'7'!J16+'8'!J16+'9'!J16+'10'!J16+'11'!J16+'12'!J16+'13'!J16+'14'!J16+'15'!J16+'16'!J16+'17'!J16+'18'!J16</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K16" s="172">
         <f>+'1'!K16+'2'!K16+'4'!K16+'3'!K16+'5'!K16+'6'!K16+'7'!K16+'8'!K16+'9'!K16+'10'!K16</f>
@@ -23551,23 +23554,23 @@
       </c>
       <c r="L16" s="175">
         <f>+'1'!L16+'2'!L16+'4'!L16+'3'!L16+'5'!L16+'6'!L16+'7'!L16+'8'!L16+'9'!L16+'10'!L16</f>
-        <v>251.82</v>
+        <v>83.94</v>
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>2895.93</v>
+        <v>965.31</v>
       </c>
       <c r="N16" s="101">
         <f>+'1'!N16+'2'!N16+'4'!N16+'3'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16</f>
-        <v>590.30804999999998</v>
+        <v>223.90995000000001</v>
       </c>
       <c r="O16" s="101">
         <f>+'1'!O16+'2'!O16+'4'!O16+'3'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16</f>
-        <v>63.371552250000001</v>
+        <v>5.9460997500000001</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="0">M16+N16+O16</f>
-        <v>3549.6096022500001</v>
+        <v>1195.16604975</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="T16" s="163" t="str">
@@ -23576,7 +23579,7 @@
       </c>
       <c r="U16" s="164">
         <f>+'3'!P35</f>
-        <v>501.4164864</v>
+        <v>0</v>
       </c>
       <c r="XFD16" t="s">
         <v>82</v>
@@ -23609,15 +23612,15 @@
       <c r="G17" s="114"/>
       <c r="H17" s="172">
         <f>+'1'!H17+'2'!H17+'4'!H17+'3'!H17+'5'!H17+'6'!H17+'7'!H17+'8'!H17+'9'!H17+'10'!H17+'11'!H17+'12'!H17+'13'!H17+'14'!H17+'15'!H17+'16'!H17</f>
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" ref="I17:I23" si="1">(G17*D17)*F17+H17*F17</f>
-        <v>6295.5</v>
+        <v>2098.5</v>
       </c>
       <c r="J17" s="172">
         <f>+'1'!J17+'2'!J17+'4'!J17+'3'!J17+'5'!J17+'6'!J17+'7'!J17+'8'!J17+'9'!J17+'10'!J17+'11'!J17+'12'!J17+'13'!J17+'14'!J17+'15'!J17+'16'!J17+'17'!J17+'18'!J17</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K17" s="172">
         <f>+'1'!K17+'2'!K17+'4'!K17+'3'!K17+'5'!K17+'6'!K17+'7'!K17+'8'!K17+'9'!K17+'10'!K17</f>
@@ -23625,23 +23628,23 @@
       </c>
       <c r="L17" s="175">
         <f>+'1'!L17+'2'!L17+'4'!L17+'3'!L17+'5'!L17+'6'!L17+'7'!L17+'8'!L17+'9'!L17+'10'!L17</f>
-        <v>503.64</v>
+        <v>167.88</v>
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="2">I17-K17-L17</f>
-        <v>5791.86</v>
+        <v>1930.62</v>
       </c>
       <c r="N17" s="101">
         <f>+'1'!N17+'2'!N17+'4'!N17+'3'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17</f>
-        <v>1180.6161</v>
+        <v>447.81990000000002</v>
       </c>
       <c r="O17" s="101">
         <f>+'1'!O17+'2'!O17+'4'!O17+'3'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17</f>
-        <v>126.7431045</v>
+        <v>11.8921995</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="0"/>
-        <v>7099.2192045000002</v>
+        <v>2390.3320994999999</v>
       </c>
       <c r="S17" s="64"/>
       <c r="T17" s="163" t="str">
@@ -23650,7 +23653,7 @@
       </c>
       <c r="U17" s="164">
         <f>+'4'!P35</f>
-        <v>1795.4904090000002</v>
+        <v>0</v>
       </c>
       <c r="XFD17" t="s">
         <v>83</v>
@@ -23723,7 +23726,7 @@
       </c>
       <c r="U18" s="164">
         <f>+'5'!P35</f>
-        <v>16843.275169500001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23753,15 +23756,15 @@
       <c r="G19" s="114"/>
       <c r="H19" s="172">
         <f>+'1'!H19+'2'!H19+'4'!H19+'3'!H19+'5'!H19+'6'!H19+'7'!H19+'8'!H19+'9'!H19+'10'!H19+'11'!H19+'12'!H19+'13'!H19+'14'!H19+'15'!H19+'16'!H19</f>
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="1"/>
-        <v>8862.08</v>
+        <v>5811.2</v>
       </c>
       <c r="J19" s="172">
         <f>+'1'!J19+'2'!J19+'4'!J19+'3'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K19" s="172">
         <f>+'1'!K19+'2'!K19+'4'!K19+'3'!K19+'5'!K19+'6'!K19+'7'!K19+'8'!K19+'9'!K19+'10'!K19</f>
@@ -23769,23 +23772,23 @@
       </c>
       <c r="L19" s="175">
         <f>+'1'!L19+'2'!L19+'4'!L19+'3'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19</f>
-        <v>708.96640000000002</v>
+        <v>464.89600000000002</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="2"/>
-        <v>8153.1135999999997</v>
+        <v>5346.3040000000001</v>
       </c>
       <c r="N19" s="101">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>1776.832512</v>
+        <v>1240.1100799999999</v>
       </c>
       <c r="O19" s="101">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>116.5203712</v>
+        <v>32.932070400000001</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="0"/>
-        <v>10046.4664832</v>
+        <v>6619.3461504000006</v>
       </c>
       <c r="T19" s="163" t="str">
         <f>+'6'!A5</f>
@@ -23793,7 +23796,7 @@
       </c>
       <c r="U19" s="164">
         <f>+'6'!P35</f>
-        <v>1795.4904090000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23823,15 +23826,15 @@
       <c r="G20" s="114"/>
       <c r="H20" s="172">
         <f>+'1'!H20+'2'!H20+'4'!H20+'3'!H20+'5'!H20+'6'!H20+'7'!H20+'8'!H20+'9'!H20+'10'!H20+'11'!H20+'12'!H20+'13'!H20+'14'!H20+'15'!H20+'16'!H20</f>
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="1"/>
-        <v>8135.68</v>
+        <v>5084.8</v>
       </c>
       <c r="J20" s="172">
         <f>+'1'!J20+'2'!J20+'4'!J20+'3'!J20+'5'!J20+'6'!J20+'7'!J20+'8'!J20+'9'!J20+'10'!J20+'11'!J20+'12'!J20+'13'!J20+'14'!J20+'15'!J20+'16'!J20+'17'!J20+'18'!J20</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K20" s="172">
         <f>+'1'!K20+'2'!K20+'4'!K20+'3'!K20+'5'!K20+'6'!K20+'7'!K20+'8'!K20+'9'!K20+'10'!K20</f>
@@ -23839,23 +23842,23 @@
       </c>
       <c r="L20" s="175">
         <f>+'1'!L20+'2'!L20+'4'!L20+'3'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20</f>
-        <v>650.85440000000006</v>
+        <v>406.78399999999999</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="2"/>
-        <v>7484.8256000000001</v>
+        <v>4678.0160000000005</v>
       </c>
       <c r="N20" s="101">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>1613.828352</v>
+        <v>1077.10592</v>
       </c>
       <c r="O20" s="101">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>112.36391040000001</v>
+        <v>28.775609600000003</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="0"/>
-        <v>9211.0178624</v>
+        <v>5783.8975296000008</v>
       </c>
       <c r="T20" s="163" t="str">
         <f>+'7'!A5</f>
@@ -23893,15 +23896,15 @@
       <c r="G21" s="114"/>
       <c r="H21" s="172">
         <f>+'1'!H21+'2'!H21+'4'!H21+'3'!H21+'5'!H21+'6'!H21+'7'!H21+'8'!H21+'9'!H21+'10'!H21+'11'!H21+'12'!H21+'13'!H21+'14'!H21+'15'!H21+'16'!H21</f>
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="1"/>
-        <v>8135.68</v>
+        <v>5084.8</v>
       </c>
       <c r="J21" s="172">
         <f>+'1'!J21+'2'!J21+'4'!J21+'3'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K21" s="172">
         <f>+'1'!K21+'2'!K21+'4'!K21+'3'!K21+'5'!K21+'6'!K21+'7'!K21+'8'!K21+'9'!K21+'10'!K21</f>
@@ -23909,23 +23912,23 @@
       </c>
       <c r="L21" s="175">
         <f>+'1'!L21+'2'!L21+'4'!L21+'3'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21</f>
-        <v>650.85440000000006</v>
+        <v>406.78399999999999</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="2"/>
-        <v>7484.8256000000001</v>
+        <v>4678.0160000000005</v>
       </c>
       <c r="N21" s="101">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>1629.8091519999998</v>
+        <v>1093.0867199999998</v>
       </c>
       <c r="O21" s="101">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>112.44381440000001</v>
+        <v>28.855513600000002</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="0"/>
-        <v>9227.0785663999995</v>
+        <v>5799.9582336000012</v>
       </c>
       <c r="T21" s="163" t="str">
         <f>+'8'!A5</f>
@@ -23963,11 +23966,11 @@
       <c r="G22" s="114"/>
       <c r="H22" s="172">
         <f>+'1'!H22+'2'!H22+'4'!H22+'3'!H22+'5'!H22+'6'!H22+'7'!H22+'8'!H22+'9'!H22+'10'!H22+'11'!H22+'12'!H22+'13'!H22+'14'!H22+'15'!H22+'16'!H22</f>
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" si="1"/>
-        <v>4707.6000000000004</v>
+        <v>1569.2000000000003</v>
       </c>
       <c r="J22" s="172">
         <f>+'1'!J22+'2'!J22+'4'!J22+'3'!J22+'5'!J22+'6'!J22+'7'!J22+'8'!J22+'9'!J22+'10'!J22+'11'!J22+'12'!J22+'13'!J22+'14'!J22+'15'!J22+'16'!J22+'17'!J22+'18'!J22</f>
@@ -23975,27 +23978,27 @@
       </c>
       <c r="K22" s="172">
         <f>+'1'!K22+'2'!K22+'4'!K22+'3'!K22+'5'!K22+'6'!K22+'7'!K22+'8'!K22+'9'!K22+'10'!K22</f>
-        <v>164.76600000000002</v>
+        <v>54.922000000000011</v>
       </c>
       <c r="L22" s="175">
         <f>+'1'!L22+'2'!L22+'4'!L22+'3'!L22+'5'!L22+'6'!L22+'7'!L22+'8'!L22+'9'!L22+'10'!L22</f>
-        <v>235.38000000000005</v>
+        <v>78.460000000000022</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="2"/>
-        <v>4307.4540000000006</v>
+        <v>1435.8180000000002</v>
       </c>
       <c r="N22" s="101">
         <f>+'1'!N22+'2'!N22+'4'!N22+'3'!N22+'5'!N22+'6'!N22+'7'!N22+'8'!N22+'9'!N22+'10'!N22</f>
-        <v>947.63988000000018</v>
+        <v>315.87996000000004</v>
       </c>
       <c r="O22" s="101">
         <f>+'1'!O22+'2'!O22+'4'!O22+'3'!O22+'5'!O22+'6'!O22+'7'!O22+'8'!O22+'9'!O22+'10'!O22</f>
-        <v>96.343387800000016</v>
+        <v>8.7584898000000013</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="0"/>
-        <v>5351.4372678</v>
+        <v>1760.4564498000002</v>
       </c>
       <c r="T22" s="163" t="str">
         <f>+'9'!A5</f>
@@ -24153,7 +24156,7 @@
       <c r="B25" s="210"/>
       <c r="C25" s="211">
         <f>H25/40</f>
-        <v>16.149999999999999</v>
+        <v>8</v>
       </c>
       <c r="D25" s="205"/>
       <c r="E25" s="205"/>
@@ -24164,39 +24167,39 @@
       </c>
       <c r="H25" s="177">
         <f t="shared" si="3"/>
-        <v>646</v>
+        <v>320</v>
       </c>
       <c r="I25" s="178">
         <f t="shared" si="3"/>
-        <v>39284.29</v>
+        <v>20697.75</v>
       </c>
       <c r="J25" s="177">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="K25" s="178">
         <f t="shared" si="3"/>
-        <v>164.76600000000002</v>
+        <v>54.922000000000011</v>
       </c>
       <c r="L25" s="179">
         <f t="shared" si="3"/>
-        <v>3001.5152000000003</v>
+        <v>1608.7440000000001</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="3"/>
-        <v>36118.008799999996</v>
+        <v>19034.083999999999</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>7739.0340460000007</v>
+        <v>4397.9125299999996</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>627.78614055000003</v>
+        <v>117.15998265000002</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>44484.828986550005</v>
+        <v>23549.156512650003</v>
       </c>
       <c r="T25" s="163" t="str">
         <f>+'12'!A5</f>
@@ -24326,7 +24329,7 @@
       </c>
       <c r="U30" s="165">
         <f>SUM(U14:U28)</f>
-        <v>44484.828986550005</v>
+        <v>23549.156512649999</v>
       </c>
     </row>
     <row r="31" spans="1:21 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24359,7 +24362,7 @@
       <c r="O32" s="222"/>
       <c r="P32" s="152">
         <f>I25</f>
-        <v>39284.29</v>
+        <v>20697.75</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24380,7 +24383,7 @@
       <c r="O33" s="224"/>
       <c r="P33" s="153">
         <f>L25</f>
-        <v>3001.5152000000003</v>
+        <v>1608.7440000000001</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24401,7 +24404,7 @@
       <c r="O34" s="224"/>
       <c r="P34" s="154">
         <f>K25</f>
-        <v>164.76600000000002</v>
+        <v>54.922000000000011</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24423,7 +24426,7 @@
       <c r="O35" s="224"/>
       <c r="P35" s="153">
         <f>P32-P33-P34</f>
-        <v>36118.008799999996</v>
+        <v>19034.084000000003</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24448,7 +24451,7 @@
       </c>
       <c r="P36" s="153">
         <f>N25</f>
-        <v>7739.0340460000007</v>
+        <v>4397.9125299999996</v>
       </c>
     </row>
     <row r="37" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24470,7 +24473,7 @@
       <c r="O37" s="226"/>
       <c r="P37" s="153">
         <f>P35+P36</f>
-        <v>43857.042845999997</v>
+        <v>23431.996530000004</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24495,7 +24498,7 @@
       </c>
       <c r="P38" s="153">
         <f>O38*P37</f>
-        <v>1096.4260711499999</v>
+        <v>585.79991325000015</v>
       </c>
     </row>
     <row r="39" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24505,7 +24508,7 @@
       <c r="O39" s="204"/>
       <c r="P39" s="160">
         <f>P37+P38</f>
-        <v>44953.468917149999</v>
+        <v>24017.796443250005</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24677,7 +24680,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -24705,7 +24708,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -25920,7 +25923,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -25948,7 +25951,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -27151,7 +27154,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -27179,7 +27182,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -27649,12 +27652,10 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="114"/>
-      <c r="H19" s="115">
-        <v>2</v>
-      </c>
+      <c r="H19" s="115"/>
       <c r="I19" s="116">
         <f t="shared" si="2"/>
-        <v>145.28</v>
+        <v>0</v>
       </c>
       <c r="J19" s="117"/>
       <c r="K19" s="1">
@@ -27663,23 +27664,23 @@
       </c>
       <c r="L19" s="105">
         <f t="shared" si="4"/>
-        <v>11.622400000000001</v>
+        <v>0</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="5"/>
-        <v>133.6576</v>
+        <v>0</v>
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>29.404672000000001</v>
+        <v>0</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="6"/>
-        <v>4.0765568000000005</v>
+        <v>0</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="1"/>
-        <v>167.1388288</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -27707,12 +27708,10 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="114"/>
-      <c r="H20" s="115">
-        <v>2</v>
-      </c>
+      <c r="H20" s="115"/>
       <c r="I20" s="116">
         <f t="shared" si="2"/>
-        <v>145.28</v>
+        <v>0</v>
       </c>
       <c r="J20" s="117"/>
       <c r="K20" s="1">
@@ -27721,23 +27720,23 @@
       </c>
       <c r="L20" s="105">
         <f t="shared" si="4"/>
-        <v>11.622400000000001</v>
+        <v>0</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="5"/>
-        <v>133.6576</v>
+        <v>0</v>
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>29.404672000000001</v>
+        <v>0</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="6"/>
-        <v>4.0765568000000005</v>
+        <v>0</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="1"/>
-        <v>167.1388288</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -27765,12 +27764,10 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="114"/>
-      <c r="H21" s="115">
-        <v>2</v>
-      </c>
+      <c r="H21" s="115"/>
       <c r="I21" s="116">
         <f t="shared" si="2"/>
-        <v>145.28</v>
+        <v>0</v>
       </c>
       <c r="J21" s="117"/>
       <c r="K21" s="1">
@@ -27779,23 +27776,23 @@
       </c>
       <c r="L21" s="105">
         <f t="shared" si="4"/>
-        <v>11.622400000000001</v>
+        <v>0</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="5"/>
-        <v>133.6576</v>
+        <v>0</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>29.404672000000001</v>
+        <v>0</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>4.0765568000000005</v>
+        <v>0</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>167.1388288</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -27981,11 +27978,11 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>435.84000000000003</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
@@ -27994,23 +27991,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>34.867200000000004</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>400.97280000000001</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>88.214016000000001</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>12.229670400000002</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>501.4164864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -28060,7 +28057,7 @@
       <c r="O28" s="222"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>435.84000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28081,7 +28078,7 @@
       <c r="O29" s="224"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>34.867200000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28124,7 +28121,7 @@
       <c r="O31" s="224"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>400.97280000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28149,7 +28146,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>88.214016000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28171,7 +28168,7 @@
       <c r="O33" s="226"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>489.18681600000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -28196,7 +28193,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>12.229670400000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -28206,7 +28203,7 @@
       <c r="O35" s="204"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>501.4164864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -28377,7 +28374,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -28405,7 +28402,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -29043,37 +29040,35 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="114"/>
-      <c r="H22" s="115">
-        <v>40</v>
-      </c>
+      <c r="H22" s="115"/>
       <c r="I22" s="116">
         <f t="shared" si="2"/>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
       <c r="J22" s="117"/>
       <c r="K22" s="1">
         <f>I22*3.5%</f>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
       <c r="L22" s="120">
         <f>I22*5%</f>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>1435.8180000000002</v>
+        <v>0</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>315.87996000000004</v>
+        <v>0</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>43.792449000000005</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>1795.4904090000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" hidden="1" x14ac:dyDescent="0.35">
@@ -29203,36 +29198,36 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>1435.8180000000002</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>315.87996000000004</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>43.792449000000005</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>1795.4904090000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -29282,7 +29277,7 @@
       <c r="O28" s="222"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29303,7 +29298,7 @@
       <c r="O29" s="224"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29324,7 +29319,7 @@
       <c r="O30" s="224"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29346,7 +29341,7 @@
       <c r="O31" s="224"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>1435.8180000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29371,7 +29366,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>315.87996000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29393,7 +29388,7 @@
       <c r="O33" s="226"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>1751.6979600000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -29418,7 +29413,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>43.792449000000005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -29428,7 +29423,7 @@
       <c r="O35" s="204"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>1795.4904090000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -29529,7 +29524,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:XFD37"/>
+  <dimension ref="A1:XFD37"/>
   <sheetFormatPr defaultColWidth="29.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.453125" customWidth="1"/>
@@ -29547,10 +29542,15 @@
     <col min="14" max="14" width="10" style="69" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.7265625" customWidth="1"/>
-    <col min="17" max="17" width="4.54296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.36328125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="7.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
+      <c r="L1" t="s">
+        <v>122</v>
+      </c>
+    </row>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
       <c r="A2" s="245" t="s">
         <v>45</v>
@@ -29600,7 +29600,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -29628,7 +29628,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -29922,41 +29922,39 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="100"/>
-      <c r="H16" s="101">
-        <v>40</v>
-      </c>
+      <c r="H16" s="101"/>
       <c r="I16" s="102">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>2098.5</v>
-      </c>
-      <c r="J16" s="103">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J16" s="103"/>
       <c r="K16" s="104">
         <f>I16*$K$13</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
         <f>I16*8%</f>
-        <v>167.88</v>
+        <v>0</v>
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>1930.62</v>
+        <v>0</v>
       </c>
       <c r="N16" s="106">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>366.3981</v>
+        <v>0</v>
       </c>
       <c r="O16" s="107">
         <f>(N16+M16)*$O$15</f>
-        <v>57.425452499999999</v>
+        <v>0</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="1">M16+N16+O16</f>
-        <v>2354.4435524999999</v>
-      </c>
-      <c r="Q16" s="108"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="64">
+        <v>40</v>
+      </c>
       <c r="XFD16" t="s">
         <v>82</v>
       </c>
@@ -29986,39 +29984,38 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="114"/>
-      <c r="H17" s="115">
-        <v>80</v>
-      </c>
+      <c r="H17" s="115"/>
       <c r="I17" s="116">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
-        <v>4197</v>
-      </c>
-      <c r="J17" s="117">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J17" s="117"/>
       <c r="K17" s="1">
         <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
         <f t="shared" ref="L17:L21" si="4">I17*8%</f>
-        <v>335.76</v>
+        <v>0</v>
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="5">I17-K17-L17</f>
-        <v>3861.24</v>
+        <v>0</v>
       </c>
       <c r="N17" s="118">
         <f t="shared" si="0"/>
-        <v>732.7962</v>
+        <v>0</v>
       </c>
       <c r="O17" s="119">
         <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
-        <v>114.850905</v>
+        <v>0</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="1"/>
-        <v>4708.8871049999998</v>
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>80</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -30106,39 +30103,38 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="114"/>
-      <c r="H19" s="115">
-        <v>40</v>
-      </c>
+      <c r="H19" s="115"/>
       <c r="I19" s="116">
         <f t="shared" si="2"/>
-        <v>2905.6</v>
-      </c>
-      <c r="J19" s="117">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J19" s="117"/>
       <c r="K19" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L19" s="105">
         <f t="shared" si="4"/>
-        <v>232.44800000000001</v>
+        <v>0</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="5"/>
-        <v>2673.152</v>
+        <v>0</v>
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>507.31775999999996</v>
+        <v>0</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="6"/>
-        <v>79.511744000000007</v>
+        <v>0</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="1"/>
-        <v>3259.9815039999999</v>
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -30166,39 +30162,38 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="114"/>
-      <c r="H20" s="115">
-        <v>40</v>
-      </c>
+      <c r="H20" s="115"/>
       <c r="I20" s="116">
         <f t="shared" si="2"/>
-        <v>2905.6</v>
-      </c>
-      <c r="J20" s="117">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J20" s="117"/>
       <c r="K20" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L20" s="105">
         <f t="shared" si="4"/>
-        <v>232.44800000000001</v>
+        <v>0</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="5"/>
-        <v>2673.152</v>
+        <v>0</v>
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>507.31775999999996</v>
+        <v>0</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="6"/>
-        <v>79.511744000000007</v>
+        <v>0</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="1"/>
-        <v>3259.9815039999999</v>
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -30226,39 +30221,38 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="114"/>
-      <c r="H21" s="115">
-        <v>40</v>
-      </c>
+      <c r="H21" s="115"/>
       <c r="I21" s="116">
         <f t="shared" si="2"/>
-        <v>2905.6</v>
-      </c>
-      <c r="J21" s="117">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J21" s="117"/>
       <c r="K21" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L21" s="105">
         <f t="shared" si="4"/>
-        <v>232.44800000000001</v>
+        <v>0</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="5"/>
-        <v>2673.152</v>
+        <v>0</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>507.31775999999996</v>
+        <v>0</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>79.511744000000007</v>
+        <v>0</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>3259.9815039999999</v>
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -30444,11 +30438,11 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>15012.300000000001</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
@@ -30457,23 +30451,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>1200.9839999999999</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>13811.315999999999</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>2621.1475799999998</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>410.81158950000003</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>16843.275169500001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -30523,7 +30517,7 @@
       <c r="O28" s="222"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>15012.300000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30544,7 +30538,7 @@
       <c r="O29" s="224"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>1200.9839999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30587,7 +30581,7 @@
       <c r="O31" s="224"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>13811.316000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30612,7 +30606,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>2621.1475799999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30634,7 +30628,7 @@
       <c r="O33" s="226"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>16432.46358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -30659,7 +30653,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>410.81158950000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -30669,7 +30663,7 @@
       <c r="O35" s="204"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>16843.275169500001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -30770,7 +30764,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:XFD37"/>
+  <dimension ref="A1:XFD37"/>
   <sheetFormatPr defaultColWidth="29.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.453125" customWidth="1"/>
@@ -30792,6 +30786,11 @@
     <col min="18" max="18" width="7.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
+      <c r="K1" t="s">
+        <v>122</v>
+      </c>
+    </row>
     <row r="2" spans="1:19 16383:16384" ht="21" x14ac:dyDescent="0.5">
       <c r="A2" s="245" t="s">
         <v>45</v>
@@ -30841,7 +30840,7 @@
       <c r="M4" s="229"/>
       <c r="N4" s="243">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="243"/>
       <c r="P4" s="243"/>
@@ -30869,7 +30868,7 @@
       <c r="M5" s="229"/>
       <c r="N5" s="243">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="230"/>
       <c r="P5" s="230"/>
@@ -31507,37 +31506,35 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="114"/>
-      <c r="H22" s="115">
-        <v>40</v>
-      </c>
+      <c r="H22" s="115"/>
       <c r="I22" s="116">
         <f t="shared" si="2"/>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
       <c r="J22" s="117"/>
       <c r="K22" s="1">
         <f>I22*3.5%</f>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
       <c r="L22" s="120">
         <f>I22*5%</f>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>1435.8180000000002</v>
+        <v>0</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>315.87996000000004</v>
+        <v>0</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>43.792449000000005</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>1795.4904090000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -31667,36 +31664,36 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>1435.8180000000002</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>315.87996000000004</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>43.792449000000005</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>1795.4904090000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -31746,7 +31743,7 @@
       <c r="O28" s="222"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31767,7 +31764,7 @@
       <c r="O29" s="224"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31788,7 +31785,7 @@
       <c r="O30" s="224"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31810,7 +31807,7 @@
       <c r="O31" s="224"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>1435.8180000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31835,7 +31832,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>315.87996000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31857,7 +31854,7 @@
       <c r="O33" s="226"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>1751.6979600000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -31882,7 +31879,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>43.792449000000005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -31892,7 +31889,7 @@
       <c r="O35" s="204"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>1795.4904090000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
